--- a/artfynd/A 51497-2025 artfynd.xlsx
+++ b/artfynd/A 51497-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481741</v>
       </c>
       <c r="B2" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Frédéric Forsmark</t>
+          <t>Frédéric Forsmark, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 51497-2025 artfynd.xlsx
+++ b/artfynd/A 51497-2025 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark, Tyr Nilsson</t>
+          <t>Tyr Nilsson, Frédéric Forsmark</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 51497-2025 artfynd.xlsx
+++ b/artfynd/A 51497-2025 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Frédéric Forsmark</t>
+          <t>Frédéric Forsmark, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 51497-2025 artfynd.xlsx
+++ b/artfynd/A 51497-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481741</v>
       </c>
       <c r="B2" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51497-2025 artfynd.xlsx
+++ b/artfynd/A 51497-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481741</v>
       </c>
       <c r="B2" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51497-2025 artfynd.xlsx
+++ b/artfynd/A 51497-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481741</v>
       </c>
       <c r="B2" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Frédéric Forsmark</t>
+          <t>Frédéric Forsmark, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 51497-2025 artfynd.xlsx
+++ b/artfynd/A 51497-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136481741</v>
       </c>
       <c r="B2" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
